--- a/data/trans_dic/IP28_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP28_R-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su peso es bastante mayor de lo normal en relación con su altura</t>
+          <t>Menores que su peso es bastante mayor de lo normal en relación con su altura (tasa de respuesta: 94,73%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,6</t>
+          <t>0,0; 4,1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,53</t>
+          <t>0,0; 6,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,65</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,27</t>
+          <t>0,0; 4,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,89</t>
+          <t>0,0; 4,76</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,47</t>
+          <t>0,0; 5,31</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,46</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,75</t>
+          <t>0,0; 3,74</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,96</t>
+          <t>0,32; 3,05</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,45; 4,02</t>
+          <t>0,43; 3,94</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,15; 3,01</t>
+          <t>0,29; 2,82</t>
         </is>
       </c>
     </row>
@@ -856,52 +857,52 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,54</t>
+          <t>0,0; 5,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,61</t>
+          <t>0,0; 4,54</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,99</t>
+          <t>0,0; 3,42</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,77</t>
+          <t>0,0; 5,65</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,71</t>
+          <t>0,0; 5,55</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,59</t>
+          <t>0,0; 5,04</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,29</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,16</t>
+          <t>0,0; 3,32</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,15</t>
+          <t>0,39; 3,47</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,44</t>
+          <t>0,36; 3,38</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -911,7 +912,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,25</t>
+          <t>0,31; 2,96</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,98</t>
+          <t>0,0; 7,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,55</t>
+          <t>0,0; 4,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,11</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,78</t>
+          <t>0,0; 1,57</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,6; 5,57</t>
+          <t>0,6; 6,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,81; 7,13</t>
+          <t>0,79; 6,91</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,96; 9,16</t>
+          <t>0,96; 8,93</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,73; 4,59</t>
+          <t>0,73; 4,24</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,29</t>
+          <t>0,46; 4,28</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,52; 5,3</t>
+          <t>0,52; 5,05</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,72</t>
+          <t>0,0; 0,64</t>
         </is>
       </c>
     </row>
@@ -1136,32 +1137,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,75</t>
+          <t>0,3; 2,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,07; 4,55</t>
+          <t>0,79; 4,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,59; 3,55</t>
+          <t>0,61; 3,5</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,25; 3,06</t>
+          <t>0,21; 2,86</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,43</t>
+          <t>0,34; 3,39</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,89; 4,22</t>
+          <t>0,9; 4,2</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1171,27 +1172,27 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,24</t>
+          <t>0,0; 2,06</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,52; 2,34</t>
+          <t>0,52; 2,5</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,22; 3,81</t>
+          <t>1,29; 3,6</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,52; 2,46</t>
+          <t>0,49; 2,32</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,78</t>
+          <t>0,32; 2,02</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,69; 6,63</t>
+          <t>0,63; 6,79</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,94; 5,44</t>
+          <t>0,96; 5,6</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,12</t>
+          <t>0,0; 4,19</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,89; 7,21</t>
+          <t>0,7; 7,57</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
+          <t>0,0; 2,56</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,47; 5,02</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>0,49; 4,11</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>0,0; 3,07</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,46; 4,58</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>0,49; 4,04</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 3,02</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,56; 3,38</t>
+          <t>0,57; 3,36</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,05; 4,29</t>
+          <t>1,01; 4,18</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,53; 3,1</t>
+          <t>0,53; 3,13</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,73; 4,0</t>
+          <t>0,77; 3,74</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,83</t>
+          <t>0,0; 6,9</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,8</t>
+          <t>0,0; 8,69</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,96</t>
+          <t>0,0; 5,39</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,05</t>
+          <t>0,0; 9,1</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,84</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,11</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,68; 10,03</t>
+          <t>0,66; 8,52</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,01</t>
+          <t>0,0; 3,49</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,14</t>
+          <t>0,0; 4,16</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,52</t>
+          <t>0,0; 2,85</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,82; 6,35</t>
+          <t>0,72; 6,34</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,76; 2,38</t>
+          <t>0,71; 2,19</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,21; 3,01</t>
+          <t>1,18; 3,11</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,47; 1,81</t>
+          <t>0,43; 1,7</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,76; 2,62</t>
+          <t>0,76; 2,6</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,04</t>
+          <t>0,69; 2,05</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,07; 2,75</t>
+          <t>1,06; 2,78</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,7</t>
+          <t>0,5; 1,72</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,51; 1,86</t>
+          <t>0,47; 1,76</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,83; 1,86</t>
+          <t>0,82; 1,9</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,31; 2,54</t>
+          <t>1,27; 2,49</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,58; 1,45</t>
+          <t>0,57; 1,44</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,77; 1,84</t>
+          <t>0,77; 1,82</t>
         </is>
       </c>
     </row>
@@ -1638,4 +1639,1622 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que su peso es bastante mayor de lo normal en relación con su altura (tasa de respuesta: 94,73%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>778</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1514</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>933</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1349</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1361</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1567</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>2127</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>2875</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>2499</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4144</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5405</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4834</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4614</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4489</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5120</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>638; 6046</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>719; 6607</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>687; 6762</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>661</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>790</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>573</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1495</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1345</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>1371</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>596</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>2161</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>573</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>2092</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4412</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3898</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3257</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 5345</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4736</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4386</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3148</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>661; 5895</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>616; 5852</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2899</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>588; 5616</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>1339</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>764</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1997</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>2077</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2680</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>3335</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>2841</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>2680</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4794</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3228</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 805</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>591; 6004</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>613; 5370</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>668; 6238</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>1206; 7015</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>710; 6552</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>670; 6475</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0; 737</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>1891</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>4209</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>3277</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2106</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>2792</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>4362</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1365</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1394</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>4683</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>8572</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>4641</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>3500</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>593; 5048</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>1478; 8836</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>1244; 7077</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>467; 6220</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>679; 6770</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>1867; 8676</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4743</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4444</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>2073; 9956</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>5100; 14197</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>1923; 9052</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>1369; 8763</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>2737</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>3418</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1391</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>3644</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>648</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>2249</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>1917</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>1537</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>3386</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>5667</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>3308</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>5181</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>651; 6992</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>1290; 7526</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4936</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>834; 9037</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3247</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>611; 6583</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>620; 5206</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4998</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>1299; 7714</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>2683; 11105</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>1288; 7660</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>2166; 10546</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>1425</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1433</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>608</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>2359</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>1425</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>1433</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>608</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>3559</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>0; 5163</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4441</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3027</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>0; 6268</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>478; 6133</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>0; 5097</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>0; 5101</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3397</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>1016; 8931</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>8832</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>12129</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>5848</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>9542</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>8131</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>11419</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>5962</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>7453</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>16963</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>23548</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>11810</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>16995</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>4476; 13757</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>7313; 19190</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>2628; 10299</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>4972; 17025</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>4666; 13894</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>6973; 18274</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>3202; 10986</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>3536; 13116</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>10701; 24862</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>16161; 31725</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>7143; 17953</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>10793; 25422</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP28_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP28_R-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su peso es bastante mayor de lo normal en relación con su altura (tasa de respuesta: 94,73%)</t>
+          <t>Menores cuyo peso es bastante mayor de lo normal en relación con su altura (tasa de respuesta: 94,73%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,12 +717,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,1</t>
+          <t>0,0; 3,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,51</t>
+          <t>0,0; 6,59</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -732,17 +732,17 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,68</t>
+          <t>0,0; 4,48</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,76</t>
+          <t>0,0; 4,97</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,31</t>
+          <t>0,0; 5,53</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -752,17 +752,17 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,74</t>
+          <t>0,0; 3,71</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,05</t>
+          <t>0,32; 3,23</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,43; 3,94</t>
+          <t>0,44; 4,18</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,82</t>
+          <t>0,29; 2,98</t>
         </is>
       </c>
     </row>
@@ -857,32 +857,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,21</t>
+          <t>0,0; 3,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,54</t>
+          <t>0,0; 4,53</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,42</t>
+          <t>0,0; 3,01</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,65</t>
+          <t>0,0; 5,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,55</t>
+          <t>0,0; 5,54</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,04</t>
+          <t>0,0; 5,54</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -892,27 +892,27 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,32</t>
+          <t>0,0; 3,38</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,39; 3,47</t>
+          <t>0,39; 3,16</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,38</t>
+          <t>0,36; 3,44</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,48</t>
+          <t>0,0; 1,47</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,96</t>
+          <t>0,31; 3,01</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,11</t>
+          <t>0,0; 6,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,29</t>
+          <t>0,0; 5,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1012,22 +1012,22 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,57</t>
+          <t>0,0; 2,08</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,6; 6,13</t>
+          <t>0,6; 5,49</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,79; 6,91</t>
+          <t>0,8; 7,17</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,96; 8,93</t>
+          <t>0,95; 9,2</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1037,22 +1037,22 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,73; 4,24</t>
+          <t>0,73; 4,87</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,28</t>
+          <t>0,49; 4,51</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,52; 5,05</t>
+          <t>0,53; 4,96</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,64</t>
+          <t>0,0; 0,72</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,55</t>
+          <t>0,3; 2,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,79; 4,71</t>
+          <t>0,78; 4,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,61; 3,5</t>
+          <t>0,63; 3,44</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,21; 2,86</t>
+          <t>0,23; 2,92</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,39</t>
+          <t>0,36; 3,54</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,9; 4,2</t>
+          <t>0,86; 4,17</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,53</t>
+          <t>0,0; 2,59</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,06</t>
+          <t>0,0; 2,13</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,52; 2,5</t>
+          <t>0,48; 2,36</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,29; 3,6</t>
+          <t>1,17; 3,48</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,32</t>
+          <t>0,52; 2,41</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,02</t>
+          <t>0,29; 2,03</t>
         </is>
       </c>
     </row>
@@ -1277,22 +1277,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,63; 6,79</t>
+          <t>0,65; 6,68</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,96; 5,6</t>
+          <t>0,96; 5,96</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,19</t>
+          <t>0,0; 4,11</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,7; 7,57</t>
+          <t>0,69; 7,83</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1302,37 +1302,37 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,47; 5,02</t>
+          <t>0,46; 4,8</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,49; 4,11</t>
+          <t>0,48; 4,11</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,07</t>
+          <t>0,0; 3,0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,57; 3,36</t>
+          <t>0,57; 3,34</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,01; 4,18</t>
+          <t>0,98; 4,22</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,53; 3,13</t>
+          <t>0,52; 2,98</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,77; 3,74</t>
+          <t>0,7; 3,72</t>
         </is>
       </c>
     </row>
@@ -1417,22 +1417,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,9</t>
+          <t>0,0; 6,34</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,69</t>
+          <t>0,0; 9,36</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,39</t>
+          <t>0,0; 4,5</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,1</t>
+          <t>0,0; 8,76</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1452,27 +1452,27 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,66; 8,52</t>
+          <t>0,7; 9,98</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,49</t>
+          <t>0,0; 3,15</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,16</t>
+          <t>0,0; 3,63</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,85</t>
+          <t>0,0; 2,93</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,72; 6,34</t>
+          <t>0,73; 6,17</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,71; 2,19</t>
+          <t>0,8; 2,32</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,18; 3,11</t>
+          <t>1,16; 2,99</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,43; 1,7</t>
+          <t>0,51; 1,77</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,76; 2,6</t>
+          <t>0,76; 2,54</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,05</t>
+          <t>0,68; 1,98</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,06; 2,78</t>
+          <t>1,03; 2,67</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,5; 1,72</t>
+          <t>0,42; 1,67</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,47; 1,76</t>
+          <t>0,53; 1,91</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,82; 1,9</t>
+          <t>0,84; 1,89</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,27; 2,49</t>
+          <t>1,32; 2,53</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,57; 1,44</t>
+          <t>0,59; 1,45</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,77; 1,82</t>
+          <t>0,79; 1,92</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su peso es bastante mayor de lo normal en relación con su altura (tasa de respuesta: 94,73%)</t>
+          <t>Menores cuyo peso es bastante mayor de lo normal en relación con su altura (tasa de respuesta: 94,73%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,12 +1927,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4144</t>
+          <t>0; 3951</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 5405</t>
+          <t>0; 5474</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1942,17 +1942,17 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 4834</t>
+          <t>0; 4626</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4614</t>
+          <t>0; 4819</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 4489</t>
+          <t>0; 4681</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1962,17 +1962,17 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 5120</t>
+          <t>0; 5074</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>638; 6046</t>
+          <t>639; 6397</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>719; 6607</t>
+          <t>741; 7007</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>687; 6762</t>
+          <t>703; 7145</t>
         </is>
       </c>
     </row>
@@ -2135,32 +2135,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4412</t>
+          <t>0; 3305</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3898</t>
+          <t>0; 3888</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 3257</t>
+          <t>0; 2866</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 5345</t>
+          <t>0; 5313</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4736</t>
+          <t>0; 4723</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 4386</t>
+          <t>0; 4823</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -2170,27 +2170,27 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 3148</t>
+          <t>0; 3202</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>661; 5895</t>
+          <t>656; 5379</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>616; 5852</t>
+          <t>629; 5948</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 2899</t>
+          <t>0; 2889</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>588; 5616</t>
+          <t>589; 5706</t>
         </is>
       </c>
     </row>
@@ -2343,12 +2343,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4794</t>
+          <t>0; 4192</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3228</t>
+          <t>0; 3808</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2358,22 +2358,22 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 805</t>
+          <t>0; 1065</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>591; 6004</t>
+          <t>591; 5381</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>613; 5370</t>
+          <t>621; 5572</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>668; 6238</t>
+          <t>666; 6430</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -2383,22 +2383,22 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1206; 7015</t>
+          <t>1209; 8058</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>710; 6552</t>
+          <t>747; 6903</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>670; 6475</t>
+          <t>681; 6355</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 737</t>
+          <t>0; 833</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>593; 5048</t>
+          <t>595; 5072</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1478; 8836</t>
+          <t>1470; 8560</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1244; 7077</t>
+          <t>1265; 6962</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>467; 6220</t>
+          <t>505; 6342</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>679; 6770</t>
+          <t>725; 7056</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1867; 8676</t>
+          <t>1774; 8615</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 4743</t>
+          <t>0; 4847</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 4444</t>
+          <t>0; 4589</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2073; 9956</t>
+          <t>1927; 9385</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5100; 14197</t>
+          <t>4595; 13718</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1923; 9052</t>
+          <t>2026; 9388</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1369; 8763</t>
+          <t>1256; 8795</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>651; 6992</t>
+          <t>670; 6873</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1290; 7526</t>
+          <t>1291; 8008</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 4936</t>
+          <t>0; 4841</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>834; 9037</t>
+          <t>824; 9354</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 3247</t>
+          <t>0; 3249</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>611; 6583</t>
+          <t>607; 6287</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>620; 5206</t>
+          <t>614; 5208</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 4998</t>
+          <t>0; 4880</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1299; 7714</t>
+          <t>1307; 7678</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2683; 11105</t>
+          <t>2602; 11189</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1288; 7660</t>
+          <t>1263; 7294</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2166; 10546</t>
+          <t>1966; 10506</t>
         </is>
       </c>
     </row>
@@ -2967,22 +2967,22 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 5163</t>
+          <t>0; 4744</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 4441</t>
+          <t>0; 4785</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 3027</t>
+          <t>0; 2531</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 6268</t>
+          <t>0; 6034</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -3002,27 +3002,27 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>478; 6133</t>
+          <t>503; 7188</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 5097</t>
+          <t>0; 4594</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0; 5101</t>
+          <t>0; 4447</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0; 3397</t>
+          <t>0; 3495</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1016; 8931</t>
+          <t>1024; 8688</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>4476; 13757</t>
+          <t>5014; 14608</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>7313; 19190</t>
+          <t>7166; 18434</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2628; 10299</t>
+          <t>3092; 10737</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4972; 17025</t>
+          <t>4954; 16608</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>4666; 13894</t>
+          <t>4621; 13408</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6973; 18274</t>
+          <t>6799; 17578</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3202; 10986</t>
+          <t>2671; 10686</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>3536; 13116</t>
+          <t>3921; 14266</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>10701; 24862</t>
+          <t>10995; 24730</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>16161; 31725</t>
+          <t>16804; 32305</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>7143; 17953</t>
+          <t>7369; 17987</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>10793; 25422</t>
+          <t>11000; 26932</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP28_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP28_R-Clase-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,62 +649,62 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1,19%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>0,77%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>1,82%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,61%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1,01%</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1,07%</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>1,72%</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1,14%</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1,07%</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>1,72%</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,11%</t>
         </is>
       </c>
     </row>
@@ -717,12 +717,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,91</t>
+          <t>0,0; 4,89</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,59</t>
+          <t>0,0; 6,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -732,12 +732,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,48</t>
+          <t>0,0; 3,99</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,97</t>
+          <t>0,0; 3,6</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -752,17 +752,17 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,71</t>
+          <t>0,0; 4,94</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,23</t>
+          <t>0,32; 2,96</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,44; 4,18</t>
+          <t>0,45; 4,02</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,98</t>
+          <t>0,27; 3,24</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>1,58%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>0,78%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>0,92%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>0,6%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1,58%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1,58%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,57%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,09%</t>
         </is>
       </c>
     </row>
@@ -857,47 +857,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,9</t>
+          <t>0,0; 4,71</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,53</t>
+          <t>0,0; 5,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,01</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,61</t>
+          <t>0,0; 2,76</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,54</t>
+          <t>0,0; 3,54</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,54</t>
+          <t>0,0; 4,61</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 2,99</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,38</t>
+          <t>0,0; 4,81</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,39; 3,16</t>
+          <t>0,0; 3,15</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -907,12 +907,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,47</t>
+          <t>0,0; 1,48</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,01</t>
+          <t>0,26; 3,27</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2,04%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2,67%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3,83%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>1,99%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>1,02%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2,04%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>2,67%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>3,83%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,45%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,22</t>
+          <t>0,6; 5,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,06</t>
+          <t>0,81; 7,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>0,96; 9,16</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,08</t>
-        </is>
-      </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,6; 5,49</t>
+          <t>0,0; 6,98</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,8; 7,17</t>
+          <t>0,0; 5,55</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,95; 9,2</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 5,11</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,73; 4,87</t>
+          <t>0,73; 4,59</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,49; 4,51</t>
+          <t>0,48; 4,29</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,53; 4,96</t>
+          <t>0,52; 5,3</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,72</t>
+          <t>0,0; 2,31</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2,11%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0,73%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0,62%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>0,96%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>2,24%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>1,62%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1,4%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,11%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,89%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,56</t>
+          <t>0,32; 3,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,78; 4,57</t>
+          <t>0,89; 4,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,63; 3,44</t>
+          <t>0,0; 2,53</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,92</t>
+          <t>0,0; 2,2</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,54</t>
+          <t>0,3; 2,75</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,86; 4,17</t>
+          <t>1,07; 4,55</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,59</t>
+          <t>0,59; 3,55</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,13</t>
+          <t>0,27; 3,61</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,36</t>
+          <t>0,52; 2,34</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,17; 3,48</t>
+          <t>1,22; 3,81</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,52; 2,41</t>
+          <t>0,52; 2,46</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,03</t>
+          <t>0,29; 1,97</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,51%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1,72%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1,04%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>2,66%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>2,54%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>1,18%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>3,05%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>1,72%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>1,51%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,65; 6,68</t>
+          <t>0,0; 3,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,96; 5,96</t>
+          <t>0,46; 4,58</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,11</t>
+          <t>0,49; 4,04</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,69; 7,83</t>
+          <t>0,0; 3,45</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,56</t>
+          <t>0,69; 6,63</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,8</t>
+          <t>0,94; 5,44</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,11</t>
+          <t>0,0; 4,12</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,0</t>
+          <t>0,96; 7,76</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,57; 3,34</t>
+          <t>0,56; 3,38</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,98; 4,22</t>
+          <t>1,05; 4,29</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,52; 2,98</t>
+          <t>0,53; 3,1</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,7; 3,72</t>
+          <t>0,79; 4,35</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>3,38%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>1,9%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>2,8%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>1,08%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>1,74%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,56%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,34</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,5</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,76</t>
+          <t>0,64; 10,54</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 6,83</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 8,8</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 5,96</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,7; 9,98</t>
+          <t>0,0; 8,43</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,15</t>
+          <t>0,0; 3,01</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,63</t>
+          <t>0,0; 4,14</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,93</t>
+          <t>0,0; 2,52</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,73; 6,17</t>
+          <t>0,89; 6,52</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1,2%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1,73%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>1,03%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>1,4%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>1,97%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>0,97%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1,46%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>1,2%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,73%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,8; 2,32</t>
+          <t>0,64; 2,04</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,16; 2,99</t>
+          <t>1,07; 2,75</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,51; 1,77</t>
+          <t>0,41; 1,7</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,76; 2,54</t>
+          <t>0,52; 1,94</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,68; 1,98</t>
+          <t>0,76; 2,38</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,03; 2,67</t>
+          <t>1,21; 3,01</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,42; 1,67</t>
+          <t>0,47; 1,81</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,53; 1,91</t>
+          <t>0,85; 2,83</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,84; 1,89</t>
+          <t>0,83; 1,86</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,32; 2,53</t>
+          <t>1,31; 2,54</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,59; 1,45</t>
+          <t>0,58; 1,45</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,79; 1,92</t>
+          <t>0,84; 2,01</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1683,7 +1683,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1791,42 +1791,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1859,62 +1859,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>1349</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1361</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1457</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>778</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>1514</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>933</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1349</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>1361</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1025</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>2127</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>2875</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>1567</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>2127</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>2875</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2499</t>
+          <t>2482</t>
         </is>
       </c>
     </row>
@@ -1927,12 +1927,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3951</t>
+          <t>0; 4737</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 5474</t>
+          <t>0; 5467</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1942,17 +1942,17 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 4626</t>
+          <t>0; 4892</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4819</t>
+          <t>0; 3642</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 4681</t>
+          <t>0; 4588</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1962,17 +1962,17 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 5074</t>
+          <t>0; 5022</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>639; 6397</t>
+          <t>636; 5850</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>741; 7007</t>
+          <t>753; 6730</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>703; 7145</t>
+          <t>611; 7259</t>
         </is>
       </c>
     </row>
@@ -1999,42 +1999,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2067,42 +2067,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1345</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1371</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>495</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>661</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>790</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>573</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1495</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1345</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1371</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>1550</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>2044</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3305</t>
+          <t>0; 4021</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3888</t>
+          <t>0; 4866</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2866</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 5313</t>
+          <t>0; 2500</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4723</t>
+          <t>0; 3000</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 4823</t>
+          <t>0; 3955</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2847</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 3202</t>
+          <t>0; 4643</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>656; 5379</t>
+          <t>0; 5364</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>629; 5948</t>
+          <t>620; 5946</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 2889</t>
+          <t>0; 2899</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>589; 5706</t>
+          <t>492; 6109</t>
         </is>
       </c>
     </row>
@@ -2207,42 +2207,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2275,62 +2275,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>1997</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2077</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2680</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>1339</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>764</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>1997</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>2077</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>492</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>3335</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>2841</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>2680</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>3335</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>2841</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>2680</t>
-        </is>
-      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>492</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4192</t>
+          <t>591; 5454</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3808</t>
+          <t>630; 5536</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>670; 6404</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0; 1065</t>
-        </is>
-      </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>591; 5381</t>
+          <t>0; 4702</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>621; 5572</t>
+          <t>0; 4175</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>666; 6430</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2688</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1209; 8058</t>
+          <t>1201; 7597</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>747; 6903</t>
+          <t>728; 6558</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>681; 6355</t>
+          <t>670; 6794</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 833</t>
+          <t>0; 2536</t>
         </is>
       </c>
     </row>
@@ -2415,42 +2415,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2483,42 +2483,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>2792</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>4362</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1365</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1232</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>1891</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>4209</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>3277</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2106</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>2792</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>4362</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>1365</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1394</t>
+          <t>2128</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>3500</t>
+          <t>3360</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>595; 5072</t>
+          <t>637; 6843</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1470; 8560</t>
+          <t>1842; 8713</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1265; 6962</t>
+          <t>0; 4748</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>505; 6342</t>
+          <t>0; 4375</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>725; 7056</t>
+          <t>597; 5452</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1774; 8615</t>
+          <t>2015; 8534</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 4847</t>
+          <t>1189; 7192</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 4589</t>
+          <t>481; 6428</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1927; 9385</t>
+          <t>2073; 9288</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4595; 13718</t>
+          <t>4810; 15033</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2026; 9388</t>
+          <t>2013; 9578</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1256; 8795</t>
+          <t>1089; 7442</t>
         </is>
       </c>
     </row>
@@ -2623,42 +2623,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2691,42 +2691,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>648</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>2249</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1917</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>1540</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>2737</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>3418</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>1391</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>3644</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>648</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>2249</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>1917</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1537</t>
+          <t>3803</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5181</t>
+          <t>5343</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>670; 6873</t>
+          <t>0; 3886</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1291; 8008</t>
+          <t>603; 5995</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 4841</t>
+          <t>617; 5117</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>824; 9354</t>
+          <t>0; 5118</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 3249</t>
+          <t>706; 6821</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>607; 6287</t>
+          <t>1262; 7307</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>614; 5208</t>
+          <t>0; 4853</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 4880</t>
+          <t>1142; 9208</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1307; 7678</t>
+          <t>1282; 7758</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2602; 11189</t>
+          <t>2786; 11374</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1263; 7294</t>
+          <t>1285; 7576</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1966; 10506</t>
+          <t>2100; 11624</t>
         </is>
       </c>
     </row>
@@ -2831,42 +2831,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -2899,42 +2899,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>2309</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>1425</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>1433</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>608</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>2359</t>
+          <t>1237</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>3559</t>
+          <t>3546</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 4744</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 4785</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 2531</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 6034</t>
+          <t>436; 7196</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 5114</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4500</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3349</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>503; 7188</t>
+          <t>0; 5928</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 4594</t>
+          <t>0; 4401</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0; 4447</t>
+          <t>0; 5075</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0; 3495</t>
+          <t>0; 3009</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1024; 8688</t>
+          <t>1227; 9045</t>
         </is>
       </c>
     </row>
@@ -3039,42 +3039,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3107,42 +3107,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>8131</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>11419</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>5962</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>7033</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>8832</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>12129</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>5848</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>9542</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>8131</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>11419</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>5962</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>7453</t>
+          <t>10234</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>16995</t>
+          <t>17268</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>5014; 14608</t>
+          <t>4311; 13812</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>7166; 18434</t>
+          <t>7023; 18104</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3092; 10737</t>
+          <t>2634; 10856</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4954; 16608</t>
+          <t>3579; 13310</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>4621; 13408</t>
+          <t>4759; 14980</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6799; 17578</t>
+          <t>7486; 18588</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2671; 10686</t>
+          <t>2820; 10946</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>3921; 14266</t>
+          <t>5265; 17464</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>10995; 24730</t>
+          <t>10838; 24355</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>16804; 32305</t>
+          <t>16690; 32343</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>7369; 17987</t>
+          <t>7182; 18092</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>11000; 26932</t>
+          <t>10927; 26226</t>
         </is>
       </c>
     </row>
